--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -8023,10 +8023,122 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1982万
+$35,332/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1547万
+$35,554/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1760万
+$37,516/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1271万
+$37,821/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1700万
+$39,171/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1880万
+$36,515/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1775万
+$35,357/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5241万
+$40,500/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U6" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+$4169万
+$42,500/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="V6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7&amp;8</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>D1 | 1612呎 (4+房)
 $6287万
@@ -8034,7 +8146,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>D2 | 1642呎 (4+房)
 $7739万
@@ -8042,7 +8154,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>D3 | 1593呎 (4+房)
 $7628万
@@ -8050,7 +8162,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D5 | 1595呎 (4+房)
 $8325万
@@ -8058,7 +8170,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>D6 | 1596呎 (4+房)
 $8330万
@@ -8066,7 +8178,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>D7 | 1602呎 (4+房)
 招标单位
@@ -8074,13 +8186,13 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr"/>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 招标单位
@@ -8088,14 +8200,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
-      <c r="Q6" s="20" t="inlineStr"/>
-      <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="20" t="inlineStr"/>
-      <c r="V6" s="23" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="23" t="inlineStr">
         <is>
           <t>S3 | 1608呎 (4+房)
 $9144万
@@ -8103,118 +8215,6 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1982万
-$35,332/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1547万
-$35,554/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1760万
-$37,516/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1271万
-$37,821/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1700万
-$39,171/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1880万
-$36,515/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1775万
-$35,357/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5241万
-$40,500/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U7" s="23" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-$4169万
-$42,500/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8639,16 +8639,100 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6065万
+$38,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4687万
+$29,200/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5834万
+$37,021/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4743万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$4978万
+$31,525/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$4752万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+$8387万
+$38,403/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6519万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1992万
@@ -8656,7 +8740,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1432万
@@ -8664,7 +8748,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1618万
@@ -8672,7 +8756,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>E5 | 298呎 (1房)
 $1010万
@@ -8680,7 +8764,7 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t>E6 | 397呎 (2房)
 $1633万
@@ -8688,7 +8772,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>E7 | 477呎 (2房)
 $1797万
@@ -8696,8 +8780,8 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr"/>
-      <c r="O12" s="21" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr"/>
+      <c r="O13" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8705,7 +8789,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1648万
@@ -8713,7 +8797,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="Q12" s="21" t="inlineStr">
+      <c r="Q13" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8721,7 +8805,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R12" s="23" t="inlineStr">
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $4670万
@@ -8729,8 +8813,8 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="23" t="inlineStr">
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5694万
@@ -8738,7 +8822,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U12" s="21" t="inlineStr">
+      <c r="U13" s="21" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8746,91 +8830,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2&amp;3</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6065万
-$38,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4687万
-$29,200/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5834万
-$37,021/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4743万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$4978万
-$31,525/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$4752万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr"/>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
-      <c r="K13" s="20" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr"/>
-      <c r="M13" s="20" t="inlineStr"/>
-      <c r="N13" s="23" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-$8387万
-$38,403/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="O13" s="20" t="inlineStr"/>
-      <c r="P13" s="20" t="inlineStr"/>
-      <c r="Q13" s="20" t="inlineStr"/>
-      <c r="R13" s="20" t="inlineStr"/>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="20" t="inlineStr"/>
-      <c r="U13" s="20" t="inlineStr"/>
-      <c r="V13" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6519万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+      <c r="V13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -6264,7 +6264,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -7577,38 +7577,30 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>37395000</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>45000</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K110" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L110" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K110" s="5" t="n">
+        <v>37395000</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>45000</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
@@ -7617,7 +7609,7 @@
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7764,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7782,7 +7774,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8023,16 +8015,100 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1612呎 (4+房)
+$6287万
+$39,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1642呎 (4+房)
+$7739万
+$47,132/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1593呎 (4+房)
+$7628万
+$47,883/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1595呎 (4+房)
+$8325万
+$52,194/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1596呎 (4+房)
+$8330万
+$52,193/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>D7 | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1608呎 (4+房)
+$9144万
+$56,866/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1982万
@@ -8040,7 +8116,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1547万
@@ -8048,7 +8124,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1760万
@@ -8056,7 +8132,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1271万
@@ -8064,7 +8140,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1700万
@@ -8072,7 +8148,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1880万
@@ -8080,8 +8156,8 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8089,7 +8165,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1775万
@@ -8097,7 +8173,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8105,7 +8181,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R6" s="21" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 招标单位
@@ -8113,8 +8189,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="23" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5241万
@@ -8122,7 +8198,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 $4169万
@@ -8130,91 +8206,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7&amp;8</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1612呎 (4+房)
-$6287万
-$39,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1642呎 (4+房)
-$7739万
-$47,132/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1593呎 (4+房)
-$7628万
-$47,883/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1595呎 (4+房)
-$8325万
-$52,194/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1596呎 (4+房)
-$8330万
-$52,193/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>D7 | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
-      <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
-      <c r="M7" s="20" t="inlineStr"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="20" t="inlineStr"/>
-      <c r="Q7" s="20" t="inlineStr"/>
-      <c r="R7" s="20" t="inlineStr"/>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="20" t="inlineStr"/>
-      <c r="V7" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1608呎 (4+房)
-$9144万
-$56,866/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8639,10 +8631,122 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1992万
+$35,499/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1432万
+$32,931/呎
+(26年-08月-14日)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1618万
+$34,490/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>E5 | 298呎 (1房)
+$1010万
+$33,903/呎
+(26年-09月-08日)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 397呎 (2房)
+$1633万
+$41,141/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M12" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 477呎 (2房)
+$1797万
+$37,665/呎
+(26年-08月-19日)</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1648万
+$32,825/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="Q12" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R12" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$4670万
+$41,143/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5694万
+$44,000/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U12" s="21" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2&amp;3</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6065万
@@ -8650,7 +8754,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4687万
@@ -8658,7 +8762,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5834万
@@ -8666,7 +8770,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4743万
@@ -8674,7 +8778,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $4978万
@@ -8682,7 +8786,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $4752万
@@ -8690,13 +8794,13 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-      <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr"/>
-      <c r="M12" s="20" t="inlineStr"/>
-      <c r="N12" s="23" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 $8387万
@@ -8704,14 +8808,14 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="20" t="inlineStr"/>
-      <c r="Q12" s="20" t="inlineStr"/>
-      <c r="R12" s="20" t="inlineStr"/>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="20" t="inlineStr"/>
-      <c r="U12" s="20" t="inlineStr"/>
-      <c r="V12" s="23" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr"/>
+      <c r="V13" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6519万
@@ -8720,172 +8824,18 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1992万
-$35,499/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1432万
-$32,931/呎
-(26年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1618万
-$34,490/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K13" s="23" t="inlineStr">
-        <is>
-          <t>E5 | 298呎 (1房)
-$1010万
-$33,903/呎
-(26年-08月-12日)</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>E6 | 397呎 (2房)
-$1633万
-$41,141/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M13" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 477呎 (2房)
-$1797万
-$37,665/呎
-(26年-08月-19日)</t>
-        </is>
-      </c>
-      <c r="N13" s="20" t="inlineStr"/>
-      <c r="O13" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P13" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1648万
-$32,825/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="Q13" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R13" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$4670万
-$41,143/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5694万
-$44,000/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U13" s="21" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V13" s="20" t="inlineStr"/>
-    </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8897,7 +8847,14 @@
       <c r="P14" s="20" t="inlineStr"/>
       <c r="Q14" s="20" t="inlineStr"/>
       <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="20" t="inlineStr"/>
+      <c r="S14" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8905,15 +8862,57 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="20" t="inlineStr"/>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H15" s="20" t="inlineStr"/>
       <c r="I15" s="20" t="inlineStr"/>
       <c r="J15" s="20" t="inlineStr"/>
@@ -8925,14 +8924,7 @@
       <c r="P15" s="20" t="inlineStr"/>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -9014,12 +9006,12 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="Q17" s="21" t="inlineStr">
+      <c r="Q17" s="23" t="inlineStr">
         <is>
           <t>G5 | 831呎 (3房)
-招标单位
--
-(在售)</t>
+$3740万
+$45,000/呎
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="R17" s="23" t="inlineStr">

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -5049,38 +5049,30 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>34720000</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>40000</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K70" s="5" t="n">
+        <v>34720000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>40000</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
@@ -5089,7 +5081,7 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7756,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7774,7 +7766,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8323,16 +8315,100 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6384万
+$40,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4815万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5358万
+$34,000/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4933万
+$31,200/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$5211万
+$33,000/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$6019万
+$38,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2185呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6678万
+$42,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1905万
@@ -8340,7 +8416,7 @@
 (26年-07月-27日)</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1487万
@@ -8348,7 +8424,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1547万
@@ -8356,7 +8432,7 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1222万
@@ -8364,7 +8440,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L9" s="22" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1634万
@@ -8372,7 +8448,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1807万
@@ -8380,8 +8456,8 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="23" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 $4002万
@@ -8389,7 +8465,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="P9" s="23" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1710万
@@ -8397,7 +8473,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8405,7 +8481,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R9" s="23" t="inlineStr">
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $3859万
@@ -8413,8 +8489,8 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="23" t="inlineStr">
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5823万
@@ -8422,7 +8498,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U9" s="21" t="inlineStr">
+      <c r="U10" s="21" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8430,91 +8506,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5&amp;6</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6384万
-$40,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4815万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5358万
-$34,000/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4933万
-$31,200/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$5211万
-$33,000/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$6019万
-$38,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2185呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-      <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr"/>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="20" t="inlineStr"/>
-      <c r="U10" s="20" t="inlineStr"/>
-      <c r="V10" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6678万
-$42,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
+      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8593,12 +8585,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="Q11" s="21" t="inlineStr">
+      <c r="Q11" s="23" t="inlineStr">
         <is>
           <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
+$3472万
+$40,000/呎
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
@@ -8631,16 +8623,100 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6065万
+$38,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4687万
+$29,200/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5834万
+$37,021/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4743万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$4978万
+$31,525/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$4752万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+$8387万
+$38,403/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6519万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1992万
@@ -8648,7 +8724,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1432万
@@ -8656,7 +8732,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1618万
@@ -8664,7 +8740,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>E5 | 298呎 (1房)
 $1010万
@@ -8672,7 +8748,7 @@
 (26年-09月-08日)</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t>E6 | 397呎 (2房)
 $1633万
@@ -8680,7 +8756,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>E7 | 477呎 (2房)
 $1797万
@@ -8688,8 +8764,8 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr"/>
-      <c r="O12" s="21" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr"/>
+      <c r="O13" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8697,7 +8773,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1648万
@@ -8705,7 +8781,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="Q12" s="21" t="inlineStr">
+      <c r="Q13" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8713,7 +8789,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R12" s="23" t="inlineStr">
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $4670万
@@ -8721,8 +8797,8 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="23" t="inlineStr">
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5694万
@@ -8730,7 +8806,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U12" s="21" t="inlineStr">
+      <c r="U13" s="21" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8738,91 +8814,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2&amp;3</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6065万
-$38,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4687万
-$29,200/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5834万
-$37,021/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4743万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$4978万
-$31,525/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$4752万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr"/>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
-      <c r="K13" s="20" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr"/>
-      <c r="M13" s="20" t="inlineStr"/>
-      <c r="N13" s="23" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-$8387万
-$38,403/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="O13" s="20" t="inlineStr"/>
-      <c r="P13" s="20" t="inlineStr"/>
-      <c r="Q13" s="20" t="inlineStr"/>
-      <c r="R13" s="20" t="inlineStr"/>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="20" t="inlineStr"/>
-      <c r="U13" s="20" t="inlineStr"/>
-      <c r="V13" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6519万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+      <c r="V13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -8007,10 +8007,122 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1982万
+$35,332/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1547万
+$35,554/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1760万
+$37,516/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1271万
+$37,821/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1700万
+$39,171/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1880万
+$36,515/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1775万
+$35,357/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5241万
+$40,500/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U6" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+$4169万
+$42,500/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="V6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7&amp;8</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>D1 | 1612呎 (4+房)
 $6287万
@@ -8018,7 +8130,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>D2 | 1642呎 (4+房)
 $7739万
@@ -8026,7 +8138,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>D3 | 1593呎 (4+房)
 $7628万
@@ -8034,7 +8146,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D5 | 1595呎 (4+房)
 $8325万
@@ -8042,7 +8154,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>D6 | 1596呎 (4+房)
 $8330万
@@ -8050,7 +8162,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>D7 | 1602呎 (4+房)
 招标单位
@@ -8058,13 +8170,13 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr"/>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 招标单位
@@ -8072,14 +8184,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
-      <c r="Q6" s="20" t="inlineStr"/>
-      <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="20" t="inlineStr"/>
-      <c r="V6" s="23" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="23" t="inlineStr">
         <is>
           <t>S3 | 1608呎 (4+房)
 $9144万
@@ -8087,118 +8199,6 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1982万
-$35,332/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1547万
-$35,554/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1760万
-$37,516/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1271万
-$37,821/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1700万
-$39,171/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1880万
-$36,515/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1775万
-$35,357/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5241万
-$40,500/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U7" s="23" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-$4169万
-$42,500/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8315,10 +8315,122 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1905万
+$33,961/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1487万
+$34,175/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1547万
+$32,991/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1222万
+$36,354/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1634万
+$37,650/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1807万
+$35,095/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="23" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+$4002万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1710万
+$34,066/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="Q9" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$3859万
+$34,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5823万
+$45,000/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U9" s="21" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5&amp;6</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6384万
@@ -8326,7 +8438,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4815万
@@ -8334,7 +8446,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5358万
@@ -8342,7 +8454,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4933万
@@ -8350,7 +8462,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $5211万
@@ -8358,7 +8470,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $6019万
@@ -8366,13 +8478,13 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-      <c r="K9" s="20" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr"/>
-      <c r="M9" s="20" t="inlineStr"/>
-      <c r="N9" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t>G1 | 2185呎 (4+房)
 招标单位
@@ -8380,14 +8492,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="20" t="inlineStr"/>
-      <c r="Q9" s="20" t="inlineStr"/>
-      <c r="R9" s="20" t="inlineStr"/>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="20" t="inlineStr"/>
-      <c r="U9" s="20" t="inlineStr"/>
-      <c r="V9" s="23" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6678万
@@ -8395,118 +8507,6 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1905万
-$33,961/呎
-(26年-07月-27日)</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1487万
-$34,175/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1547万
-$32,991/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1222万
-$36,354/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1634万
-$37,650/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M10" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1807万
-$35,095/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="23" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-$4002万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1710万
-$34,066/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="Q10" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R10" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$3859万
-$34,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5823万
-$45,000/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U10" s="21" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8623,10 +8623,122 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1992万
+$35,499/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1432万
+$32,931/呎
+(26年-08月-14日)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1618万
+$34,490/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>E5 | 298呎 (1房)
+$1010万
+$33,903/呎
+(26年-09月-08日)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 397呎 (2房)
+$1633万
+$41,141/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M12" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 477呎 (2房)
+$1797万
+$37,665/呎
+(26年-08月-19日)</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1648万
+$32,825/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="Q12" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R12" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$4670万
+$41,143/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5694万
+$44,000/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U12" s="21" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2&amp;3</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6065万
@@ -8634,7 +8746,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4687万
@@ -8642,7 +8754,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5834万
@@ -8650,7 +8762,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4743万
@@ -8658,7 +8770,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $4978万
@@ -8666,7 +8778,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $4752万
@@ -8674,13 +8786,13 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-      <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr"/>
-      <c r="M12" s="20" t="inlineStr"/>
-      <c r="N12" s="23" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 $8387万
@@ -8688,14 +8800,14 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="20" t="inlineStr"/>
-      <c r="Q12" s="20" t="inlineStr"/>
-      <c r="R12" s="20" t="inlineStr"/>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="20" t="inlineStr"/>
-      <c r="U12" s="20" t="inlineStr"/>
-      <c r="V12" s="23" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr"/>
+      <c r="V13" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6519万
@@ -8704,122 +8816,10 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1992万
-$35,499/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1432万
-$32,931/呎
-(26年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1618万
-$34,490/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K13" s="23" t="inlineStr">
-        <is>
-          <t>E5 | 298呎 (1房)
-$1010万
-$33,903/呎
-(26年-09月-08日)</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>E6 | 397呎 (2房)
-$1633万
-$41,141/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M13" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 477呎 (2房)
-$1797万
-$37,665/呎
-(26年-08月-19日)</t>
-        </is>
-      </c>
-      <c r="N13" s="20" t="inlineStr"/>
-      <c r="O13" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P13" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1648万
-$32,825/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="Q13" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R13" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$4670万
-$41,143/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5694万
-$44,000/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U13" s="21" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V13" s="20" t="inlineStr"/>
-    </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr"/>
@@ -8836,17 +8836,31 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="20" t="inlineStr"/>
-      <c r="Q14" s="20" t="inlineStr"/>
-      <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q14" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
+      <c r="R14" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8924,7 +8938,7 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr"/>
@@ -8941,31 +8955,17 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q16" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P16" s="20" t="inlineStr"/>
+      <c r="Q16" s="20" t="inlineStr"/>
+      <c r="R16" s="20" t="inlineStr"/>
+      <c r="S16" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R16" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -8007,16 +8007,100 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1612呎 (4+房)
+$6287万
+$39,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1642呎 (4+房)
+$7739万
+$47,132/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1593呎 (4+房)
+$7628万
+$47,883/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1595呎 (4+房)
+$8325万
+$52,194/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1596呎 (4+房)
+$8330万
+$52,193/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>D7 | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1608呎 (4+房)
+$9144万
+$56,866/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1982万
@@ -8024,7 +8108,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1547万
@@ -8032,7 +8116,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1760万
@@ -8040,7 +8124,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1271万
@@ -8048,7 +8132,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1700万
@@ -8056,7 +8140,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1880万
@@ -8064,8 +8148,8 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8073,7 +8157,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1775万
@@ -8081,7 +8165,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8089,7 +8173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R6" s="21" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 招标单位
@@ -8097,8 +8181,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="23" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5241万
@@ -8106,7 +8190,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 $4169万
@@ -8114,91 +8198,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7&amp;8</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1612呎 (4+房)
-$6287万
-$39,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1642呎 (4+房)
-$7739万
-$47,132/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1593呎 (4+房)
-$7628万
-$47,883/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1595呎 (4+房)
-$8325万
-$52,194/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1596呎 (4+房)
-$8330万
-$52,193/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>D7 | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
-      <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
-      <c r="M7" s="20" t="inlineStr"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="20" t="inlineStr"/>
-      <c r="Q7" s="20" t="inlineStr"/>
-      <c r="R7" s="20" t="inlineStr"/>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="20" t="inlineStr"/>
-      <c r="V7" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1608呎 (4+房)
-$9144万
-$56,866/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8623,16 +8623,100 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6065万
+$38,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4687万
+$29,200/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5834万
+$37,021/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4743万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$4978万
+$31,525/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$4752万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+$8387万
+$38,403/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6519万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1992万
@@ -8640,7 +8724,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1432万
@@ -8648,7 +8732,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1618万
@@ -8656,7 +8740,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>E5 | 298呎 (1房)
 $1010万
@@ -8664,7 +8748,7 @@
 (26年-09月-08日)</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t>E6 | 397呎 (2房)
 $1633万
@@ -8672,7 +8756,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>E7 | 477呎 (2房)
 $1797万
@@ -8680,8 +8764,8 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr"/>
-      <c r="O12" s="21" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr"/>
+      <c r="O13" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8689,7 +8773,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1648万
@@ -8697,7 +8781,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="Q12" s="21" t="inlineStr">
+      <c r="Q13" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8705,7 +8789,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R12" s="23" t="inlineStr">
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $4670万
@@ -8713,8 +8797,8 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="23" t="inlineStr">
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5694万
@@ -8722,7 +8806,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U12" s="21" t="inlineStr">
+      <c r="U13" s="21" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8730,104 +8814,62 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2&amp;3</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6065万
-$38,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4687万
-$29,200/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5834万
-$37,021/呎
+      <c r="V13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4743万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$4978万
-$31,525/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$4752万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr"/>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
-      <c r="K13" s="20" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr"/>
-      <c r="M13" s="20" t="inlineStr"/>
-      <c r="N13" s="23" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-$8387万
-$38,403/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="O13" s="20" t="inlineStr"/>
-      <c r="P13" s="20" t="inlineStr"/>
-      <c r="Q13" s="20" t="inlineStr"/>
-      <c r="R13" s="20" t="inlineStr"/>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="20" t="inlineStr"/>
-      <c r="U13" s="20" t="inlineStr"/>
-      <c r="V13" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6519万
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
 $41,000/呎
 (26年-06月-26日)</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8836,30 +8878,9 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q14" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R14" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="P14" s="20" t="inlineStr"/>
+      <c r="Q14" s="20" t="inlineStr"/>
+      <c r="R14" s="20" t="inlineStr"/>
       <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
@@ -8868,57 +8889,15 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
       <c r="H15" s="20" t="inlineStr"/>
       <c r="I15" s="20" t="inlineStr"/>
       <c r="J15" s="20" t="inlineStr"/>
@@ -8930,7 +8909,14 @@
       <c r="P15" s="20" t="inlineStr"/>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="20" t="inlineStr"/>
+      <c r="S15" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8938,7 +8924,7 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr"/>
@@ -8955,17 +8941,31 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="20" t="inlineStr"/>
-      <c r="Q16" s="20" t="inlineStr"/>
-      <c r="R16" s="20" t="inlineStr"/>
-      <c r="S16" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q16" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
+      <c r="R16" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -8315,16 +8315,100 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6384万
+$40,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4815万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5358万
+$34,000/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4933万
+$31,200/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$5211万
+$33,000/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$6019万
+$38,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2185呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6678万
+$42,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1905万
@@ -8332,7 +8416,7 @@
 (26年-07月-27日)</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1487万
@@ -8340,7 +8424,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1547万
@@ -8348,7 +8432,7 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1222万
@@ -8356,7 +8440,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L9" s="22" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1634万
@@ -8364,7 +8448,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1807万
@@ -8372,8 +8456,8 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="23" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 $4002万
@@ -8381,7 +8465,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="P9" s="23" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1710万
@@ -8389,7 +8473,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8397,7 +8481,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R9" s="23" t="inlineStr">
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $3859万
@@ -8405,8 +8489,8 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="23" t="inlineStr">
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5823万
@@ -8414,7 +8498,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U9" s="21" t="inlineStr">
+      <c r="U10" s="21" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8422,91 +8506,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5&amp;6</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6384万
-$40,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4815万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5358万
-$34,000/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4933万
-$31,200/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$5211万
-$33,000/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$6019万
-$38,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2185呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-      <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr"/>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="20" t="inlineStr"/>
-      <c r="U10" s="20" t="inlineStr"/>
-      <c r="V10" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6678万
-$42,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
+      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8819,57 +8819,15 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8881,7 +8839,14 @@
       <c r="P14" s="20" t="inlineStr"/>
       <c r="Q14" s="20" t="inlineStr"/>
       <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="20" t="inlineStr"/>
+      <c r="S14" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8889,15 +8854,57 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="20" t="inlineStr"/>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H15" s="20" t="inlineStr"/>
       <c r="I15" s="20" t="inlineStr"/>
       <c r="J15" s="20" t="inlineStr"/>
@@ -8909,14 +8916,7 @@
       <c r="P15" s="20" t="inlineStr"/>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -8007,10 +8007,122 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1982万
+$35,332/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1547万
+$35,554/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1760万
+$37,516/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1271万
+$37,821/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1700万
+$39,171/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1880万
+$36,515/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1775万
+$35,357/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5241万
+$40,500/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U6" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+$4169万
+$42,500/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="V6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7&amp;8</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>D1 | 1612呎 (4+房)
 $6287万
@@ -8018,7 +8130,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>D2 | 1642呎 (4+房)
 $7739万
@@ -8026,7 +8138,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>D3 | 1593呎 (4+房)
 $7628万
@@ -8034,7 +8146,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D5 | 1595呎 (4+房)
 $8325万
@@ -8042,7 +8154,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>D6 | 1596呎 (4+房)
 $8330万
@@ -8050,7 +8162,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>D7 | 1602呎 (4+房)
 招标单位
@@ -8058,13 +8170,13 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr"/>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 招标单位
@@ -8072,14 +8184,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
-      <c r="Q6" s="20" t="inlineStr"/>
-      <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="20" t="inlineStr"/>
-      <c r="V6" s="23" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="23" t="inlineStr">
         <is>
           <t>S3 | 1608呎 (4+房)
 $9144万
@@ -8087,118 +8199,6 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1982万
-$35,332/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1547万
-$35,554/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1760万
-$37,516/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1271万
-$37,821/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1700万
-$39,171/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1880万
-$36,515/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1775万
-$35,357/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5241万
-$40,500/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U7" s="23" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-$4169万
-$42,500/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8819,15 +8819,57 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8839,14 +8881,7 @@
       <c r="P14" s="20" t="inlineStr"/>
       <c r="Q14" s="20" t="inlineStr"/>
       <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8854,57 +8889,15 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
       <c r="H15" s="20" t="inlineStr"/>
       <c r="I15" s="20" t="inlineStr"/>
       <c r="J15" s="20" t="inlineStr"/>
@@ -8913,9 +8906,30 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="20" t="inlineStr"/>
-      <c r="Q15" s="20" t="inlineStr"/>
-      <c r="R15" s="20" t="inlineStr"/>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q15" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
       <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
@@ -8924,7 +8938,7 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr"/>
@@ -8941,31 +8955,17 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q16" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P16" s="20" t="inlineStr"/>
+      <c r="Q16" s="20" t="inlineStr"/>
+      <c r="R16" s="20" t="inlineStr"/>
+      <c r="S16" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R16" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -8007,16 +8007,100 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1612呎 (4+房)
+$6287万
+$39,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1642呎 (4+房)
+$7739万
+$47,132/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1593呎 (4+房)
+$7628万
+$47,883/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1595呎 (4+房)
+$8325万
+$52,194/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1596呎 (4+房)
+$8330万
+$52,193/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>D7 | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1608呎 (4+房)
+$9144万
+$56,866/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1982万
@@ -8024,7 +8108,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1547万
@@ -8032,7 +8116,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1760万
@@ -8040,7 +8124,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1271万
@@ -8048,7 +8132,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1700万
@@ -8056,7 +8140,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1880万
@@ -8064,8 +8148,8 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8073,7 +8157,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1775万
@@ -8081,7 +8165,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8089,7 +8173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R6" s="21" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 招标单位
@@ -8097,8 +8181,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="23" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5241万
@@ -8106,7 +8190,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 $4169万
@@ -8114,91 +8198,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7&amp;8</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1612呎 (4+房)
-$6287万
-$39,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1642呎 (4+房)
-$7739万
-$47,132/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1593呎 (4+房)
-$7628万
-$47,883/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1595呎 (4+房)
-$8325万
-$52,194/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1596呎 (4+房)
-$8330万
-$52,193/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>D7 | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
-      <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
-      <c r="M7" s="20" t="inlineStr"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="20" t="inlineStr"/>
-      <c r="Q7" s="20" t="inlineStr"/>
-      <c r="R7" s="20" t="inlineStr"/>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="20" t="inlineStr"/>
-      <c r="V7" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1608呎 (4+房)
-$9144万
-$56,866/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8315,10 +8315,122 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1905万
+$33,961/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1487万
+$34,175/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1547万
+$32,991/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1222万
+$36,354/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1634万
+$37,650/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1807万
+$35,095/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="23" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+$4002万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1710万
+$34,066/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="Q9" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$3859万
+$34,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5823万
+$45,000/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U9" s="21" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5&amp;6</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6384万
@@ -8326,7 +8438,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4815万
@@ -8334,7 +8446,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5358万
@@ -8342,7 +8454,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4933万
@@ -8350,7 +8462,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $5211万
@@ -8358,7 +8470,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $6019万
@@ -8366,13 +8478,13 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-      <c r="K9" s="20" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr"/>
-      <c r="M9" s="20" t="inlineStr"/>
-      <c r="N9" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t>G1 | 2185呎 (4+房)
 招标单位
@@ -8380,14 +8492,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="20" t="inlineStr"/>
-      <c r="Q9" s="20" t="inlineStr"/>
-      <c r="R9" s="20" t="inlineStr"/>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="20" t="inlineStr"/>
-      <c r="U9" s="20" t="inlineStr"/>
-      <c r="V9" s="23" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6678万
@@ -8395,118 +8507,6 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1905万
-$33,961/呎
-(26年-07月-27日)</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1487万
-$34,175/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1547万
-$32,991/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1222万
-$36,354/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1634万
-$37,650/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M10" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1807万
-$35,095/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="23" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-$4002万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1710万
-$34,066/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="Q10" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R10" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$3859万
-$34,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5823万
-$45,000/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U10" s="21" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8889,7 +8889,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -8906,31 +8906,17 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q15" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P15" s="20" t="inlineStr"/>
+      <c r="Q15" s="20" t="inlineStr"/>
+      <c r="R15" s="20" t="inlineStr"/>
+      <c r="S15" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R15" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8938,7 +8924,7 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr"/>
@@ -8955,17 +8941,31 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="20" t="inlineStr"/>
-      <c r="Q16" s="20" t="inlineStr"/>
-      <c r="R16" s="20" t="inlineStr"/>
-      <c r="S16" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q16" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
+      <c r="R16" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -5054,7 +5054,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -8590,7 +8590,7 @@
           <t>G5 | 868呎 (3房)
 $3472万
 $40,000/呎
-(26年-09月-12日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="R11" s="23" t="inlineStr">
@@ -8819,57 +8819,15 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8881,7 +8839,14 @@
       <c r="P14" s="20" t="inlineStr"/>
       <c r="Q14" s="20" t="inlineStr"/>
       <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="20" t="inlineStr"/>
+      <c r="S14" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8889,7 +8854,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -8906,17 +8871,31 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="20" t="inlineStr"/>
-      <c r="Q15" s="20" t="inlineStr"/>
-      <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q15" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8924,15 +8903,57 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8941,30 +8962,9 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q16" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R16" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="P16" s="20" t="inlineStr"/>
+      <c r="Q16" s="20" t="inlineStr"/>
+      <c r="R16" s="20" t="inlineStr"/>
       <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
@@ -9003,7 +9003,7 @@
           <t>G5 | 831呎 (3房)
 $3740万
 $45,000/呎
-(26年-09月-10日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="R17" s="23" t="inlineStr">

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -8819,15 +8819,57 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8839,14 +8881,7 @@
       <c r="P14" s="20" t="inlineStr"/>
       <c r="Q14" s="20" t="inlineStr"/>
       <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8854,7 +8889,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -8871,31 +8906,17 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q15" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P15" s="20" t="inlineStr"/>
+      <c r="Q15" s="20" t="inlineStr"/>
+      <c r="R15" s="20" t="inlineStr"/>
+      <c r="S15" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R15" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8903,57 +8924,15 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8962,9 +8941,30 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="20" t="inlineStr"/>
-      <c r="Q16" s="20" t="inlineStr"/>
-      <c r="R16" s="20" t="inlineStr"/>
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q16" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R16" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
       <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -8007,10 +8007,122 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1982万
+$35,332/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1547万
+$35,554/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1760万
+$37,516/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1271万
+$37,821/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1700万
+$39,171/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1880万
+$36,515/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1775万
+$35,357/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5241万
+$40,500/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U6" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+$4169万
+$42,500/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="V6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7&amp;8</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>D1 | 1612呎 (4+房)
 $6287万
@@ -8018,7 +8130,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>D2 | 1642呎 (4+房)
 $7739万
@@ -8026,7 +8138,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>D3 | 1593呎 (4+房)
 $7628万
@@ -8034,7 +8146,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D5 | 1595呎 (4+房)
 $8325万
@@ -8042,7 +8154,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>D6 | 1596呎 (4+房)
 $8330万
@@ -8050,7 +8162,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>D7 | 1602呎 (4+房)
 招标单位
@@ -8058,13 +8170,13 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr"/>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 招标单位
@@ -8072,14 +8184,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
-      <c r="Q6" s="20" t="inlineStr"/>
-      <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="20" t="inlineStr"/>
-      <c r="V6" s="23" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="23" t="inlineStr">
         <is>
           <t>S3 | 1608呎 (4+房)
 $9144万
@@ -8087,118 +8199,6 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1982万
-$35,332/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1547万
-$35,554/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1760万
-$37,516/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1271万
-$37,821/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1700万
-$39,171/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1880万
-$36,515/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1775万
-$35,357/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5241万
-$40,500/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U7" s="23" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-$4169万
-$42,500/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8819,57 +8819,15 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8881,7 +8839,14 @@
       <c r="P14" s="20" t="inlineStr"/>
       <c r="Q14" s="20" t="inlineStr"/>
       <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="20" t="inlineStr"/>
+      <c r="S14" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8889,7 +8854,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -8906,17 +8871,31 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="20" t="inlineStr"/>
-      <c r="Q15" s="20" t="inlineStr"/>
-      <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q15" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8924,15 +8903,57 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8941,30 +8962,9 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q16" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R16" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="P16" s="20" t="inlineStr"/>
+      <c r="Q16" s="20" t="inlineStr"/>
+      <c r="R16" s="20" t="inlineStr"/>
       <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -8007,16 +8007,100 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1612呎 (4+房)
+$6287万
+$39,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1642呎 (4+房)
+$7739万
+$47,132/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1593呎 (4+房)
+$7628万
+$47,883/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1595呎 (4+房)
+$8325万
+$52,194/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1596呎 (4+房)
+$8330万
+$52,193/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>D7 | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1608呎 (4+房)
+$9144万
+$56,866/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1982万
@@ -8024,7 +8108,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1547万
@@ -8032,7 +8116,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1760万
@@ -8040,7 +8124,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1271万
@@ -8048,7 +8132,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1700万
@@ -8056,7 +8140,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1880万
@@ -8064,8 +8148,8 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8073,7 +8157,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1775万
@@ -8081,7 +8165,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8089,7 +8173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R6" s="21" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 招标单位
@@ -8097,8 +8181,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="23" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5241万
@@ -8106,7 +8190,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 $4169万
@@ -8114,91 +8198,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7&amp;8</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1612呎 (4+房)
-$6287万
-$39,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1642呎 (4+房)
-$7739万
-$47,132/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1593呎 (4+房)
-$7628万
-$47,883/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1595呎 (4+房)
-$8325万
-$52,194/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1596呎 (4+房)
-$8330万
-$52,193/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>D7 | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
-      <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
-      <c r="M7" s="20" t="inlineStr"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="20" t="inlineStr"/>
-      <c r="Q7" s="20" t="inlineStr"/>
-      <c r="R7" s="20" t="inlineStr"/>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="20" t="inlineStr"/>
-      <c r="V7" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1608呎 (4+房)
-$9144万
-$56,866/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8623,10 +8623,122 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1992万
+$35,499/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1432万
+$32,931/呎
+(26年-08月-14日)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1618万
+$34,490/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>E5 | 298呎 (1房)
+$1010万
+$33,903/呎
+(26年-09月-08日)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 397呎 (2房)
+$1633万
+$41,141/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M12" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 477呎 (2房)
+$1797万
+$37,665/呎
+(26年-08月-19日)</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1648万
+$32,825/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="Q12" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R12" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$4670万
+$41,143/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5694万
+$44,000/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U12" s="21" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2&amp;3</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6065万
@@ -8634,7 +8746,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4687万
@@ -8642,7 +8754,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5834万
@@ -8650,7 +8762,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4743万
@@ -8658,7 +8770,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $4978万
@@ -8666,7 +8778,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $4752万
@@ -8674,13 +8786,13 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-      <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr"/>
-      <c r="M12" s="20" t="inlineStr"/>
-      <c r="N12" s="23" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 $8387万
@@ -8688,14 +8800,14 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="20" t="inlineStr"/>
-      <c r="Q12" s="20" t="inlineStr"/>
-      <c r="R12" s="20" t="inlineStr"/>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="20" t="inlineStr"/>
-      <c r="U12" s="20" t="inlineStr"/>
-      <c r="V12" s="23" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr"/>
+      <c r="V13" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6519万
@@ -8704,130 +8816,60 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1992万
-$35,499/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1432万
-$32,931/呎
-(26年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1618万
-$34,490/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K13" s="23" t="inlineStr">
-        <is>
-          <t>E5 | 298呎 (1房)
-$1010万
-$33,903/呎
-(26年-09月-08日)</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>E6 | 397呎 (2房)
-$1633万
-$41,141/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M13" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 477呎 (2房)
-$1797万
-$37,665/呎
-(26年-08月-19日)</t>
-        </is>
-      </c>
-      <c r="N13" s="20" t="inlineStr"/>
-      <c r="O13" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P13" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1648万
-$32,825/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="Q13" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R13" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$4670万
-$41,143/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5694万
-$44,000/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U13" s="21" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V13" s="20" t="inlineStr"/>
-    </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8839,14 +8881,7 @@
       <c r="P14" s="20" t="inlineStr"/>
       <c r="Q14" s="20" t="inlineStr"/>
       <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8903,57 +8938,15 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8965,7 +8958,14 @@
       <c r="P16" s="20" t="inlineStr"/>
       <c r="Q16" s="20" t="inlineStr"/>
       <c r="R16" s="20" t="inlineStr"/>
-      <c r="S16" s="20" t="inlineStr"/>
+      <c r="S16" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -8007,10 +8007,122 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1982万
+$35,332/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1547万
+$35,554/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1760万
+$37,516/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1271万
+$37,821/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1700万
+$39,171/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1880万
+$36,515/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1775万
+$35,357/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5241万
+$40,500/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U6" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+$4169万
+$42,500/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="V6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7&amp;8</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>D1 | 1612呎 (4+房)
 $6287万
@@ -8018,7 +8130,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>D2 | 1642呎 (4+房)
 $7739万
@@ -8026,7 +8138,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>D3 | 1593呎 (4+房)
 $7628万
@@ -8034,7 +8146,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D5 | 1595呎 (4+房)
 $8325万
@@ -8042,7 +8154,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>D6 | 1596呎 (4+房)
 $8330万
@@ -8050,7 +8162,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>D7 | 1602呎 (4+房)
 招标单位
@@ -8058,13 +8170,13 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr"/>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 招标单位
@@ -8072,14 +8184,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
-      <c r="Q6" s="20" t="inlineStr"/>
-      <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="20" t="inlineStr"/>
-      <c r="V6" s="23" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="23" t="inlineStr">
         <is>
           <t>S3 | 1608呎 (4+房)
 $9144万
@@ -8087,118 +8199,6 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1982万
-$35,332/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1547万
-$35,554/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1760万
-$37,516/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1271万
-$37,821/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1700万
-$39,171/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1880万
-$36,515/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1775万
-$35,357/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5241万
-$40,500/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U7" s="23" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-$4169万
-$42,500/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8315,16 +8315,100 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6384万
+$40,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4815万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5358万
+$34,000/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4933万
+$31,200/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$5211万
+$33,000/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$6019万
+$38,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2185呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6678万
+$42,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1905万
@@ -8332,7 +8416,7 @@
 (26年-07月-27日)</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1487万
@@ -8340,7 +8424,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1547万
@@ -8348,7 +8432,7 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1222万
@@ -8356,7 +8440,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L9" s="22" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1634万
@@ -8364,7 +8448,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1807万
@@ -8372,8 +8456,8 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="23" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 $4002万
@@ -8381,7 +8465,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="P9" s="23" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1710万
@@ -8389,7 +8473,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8397,7 +8481,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R9" s="23" t="inlineStr">
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $3859万
@@ -8405,8 +8489,8 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="23" t="inlineStr">
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5823万
@@ -8414,7 +8498,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U9" s="21" t="inlineStr">
+      <c r="U10" s="21" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8422,91 +8506,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5&amp;6</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6384万
-$40,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4815万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5358万
-$34,000/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4933万
-$31,200/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$5211万
-$33,000/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$6019万
-$38,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2185呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-      <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr"/>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="20" t="inlineStr"/>
-      <c r="U10" s="20" t="inlineStr"/>
-      <c r="V10" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6678万
-$42,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
+      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">

--- a/web/files/九龙-石硖尾-滶蕴.xlsx
+++ b/web/files/九龙-石硖尾-滶蕴.xlsx
@@ -8819,57 +8819,15 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8878,9 +8836,30 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="20" t="inlineStr"/>
-      <c r="Q14" s="20" t="inlineStr"/>
-      <c r="R14" s="20" t="inlineStr"/>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q14" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R14" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
       <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
@@ -8889,7 +8868,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -8906,31 +8885,17 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q15" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P15" s="20" t="inlineStr"/>
+      <c r="Q15" s="20" t="inlineStr"/>
+      <c r="R15" s="20" t="inlineStr"/>
+      <c r="S15" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R15" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8938,15 +8903,57 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8958,14 +8965,7 @@
       <c r="P16" s="20" t="inlineStr"/>
       <c r="Q16" s="20" t="inlineStr"/>
       <c r="R16" s="20" t="inlineStr"/>
-      <c r="S16" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>
